--- a/educhrono-backend/app/templates/room-list_template_new.xlsx
+++ b/educhrono-backend/app/templates/room-list_template_new.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\FunctionX\educhrono-backend\app\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\FunctionX\educhrono\educhrono-backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A86FD3-A6DE-4B9B-A9CA-272326221BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1217C0A-E7C4-4CB4-9369-24E3A7347CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19260" windowHeight="10800" xr2:uid="{E0646FFD-B509-4CB0-B68B-24A555666CE0}"/>
+    <workbookView xWindow="100" yWindow="0" windowWidth="19100" windowHeight="10800" xr2:uid="{E0646FFD-B509-4CB0-B68B-24A555666CE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="176">
   <si>
     <t>Room No</t>
   </si>
@@ -534,6 +534,36 @@
   </si>
   <si>
     <t>CSE-260</t>
+  </si>
+  <si>
+    <t>Assigned_Semester</t>
+  </si>
+  <si>
+    <t>Assigned_Section</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Lab</t>
   </si>
 </sst>
 </file>
@@ -940,16 +970,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2743B8EA-E3D9-4591-93D1-662FDFB80557}">
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:F161"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -962,97 +994,139 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="1">
+        <v>60</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="C2" s="1">
-        <v>60</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="F2" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="1">
+        <v>60</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="C3" s="1">
-        <v>60</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="F3" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="1">
+        <v>60</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="C4" s="1">
-        <v>60</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="F4" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="1">
+        <v>60</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="C5" s="1">
-        <v>60</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="F5" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="1">
+        <v>60</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="C6" s="1">
-        <v>60</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="F6" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="1">
+        <v>60</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="C7" s="1">
-        <v>60</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="F7" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
+      <c r="B8" t="s">
+        <v>168</v>
       </c>
       <c r="C8" s="1">
         <v>60</v>
@@ -1060,13 +1134,19 @@
       <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
+      <c r="B9" t="s">
+        <v>168</v>
       </c>
       <c r="C9" s="1">
         <v>60</v>
@@ -1074,13 +1154,19 @@
       <c r="D9" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="E9">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
+      <c r="B10" t="s">
+        <v>168</v>
       </c>
       <c r="C10" s="1">
         <v>60</v>
@@ -1088,13 +1174,19 @@
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
+      <c r="B11" t="s">
+        <v>168</v>
       </c>
       <c r="C11" s="1">
         <v>60</v>
@@ -1102,13 +1194,19 @@
       <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="E11">
+        <v>7</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
+      <c r="B12" t="s">
+        <v>168</v>
       </c>
       <c r="C12" s="1">
         <v>60</v>
@@ -1116,13 +1214,19 @@
       <c r="D12" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
+      <c r="B13" t="s">
+        <v>168</v>
       </c>
       <c r="C13" s="1">
         <v>60</v>
@@ -1130,8 +1234,14 @@
       <c r="D13" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="E13">
+        <v>7</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -1145,7 +1255,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -1159,7 +1269,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1425,12 +1535,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>5</v>
+        <v>175</v>
       </c>
       <c r="C35" s="1">
         <v>60</v>
@@ -1439,12 +1549,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>5</v>
+        <v>175</v>
       </c>
       <c r="C36" s="1">
         <v>60</v>
@@ -1453,12 +1563,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>5</v>
+      <c r="B37" t="s">
+        <v>175</v>
       </c>
       <c r="C37" s="1">
         <v>60</v>
@@ -1467,12 +1577,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>5</v>
+      <c r="B38" t="s">
+        <v>175</v>
       </c>
       <c r="C38" s="1">
         <v>60</v>
@@ -1481,12 +1591,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>5</v>
+      <c r="B39" t="s">
+        <v>175</v>
       </c>
       <c r="C39" s="1">
         <v>60</v>
@@ -1495,12 +1605,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>5</v>
+      <c r="B40" t="s">
+        <v>175</v>
       </c>
       <c r="C40" s="1">
         <v>60</v>
@@ -1509,12 +1619,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>5</v>
+      <c r="B41" t="s">
+        <v>175</v>
       </c>
       <c r="C41" s="1">
         <v>60</v>
@@ -1523,12 +1633,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>5</v>
+      <c r="B42" t="s">
+        <v>175</v>
       </c>
       <c r="C42" s="1">
         <v>60</v>
@@ -1537,12 +1647,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>5</v>
+      <c r="B43" t="s">
+        <v>175</v>
       </c>
       <c r="C43" s="1">
         <v>60</v>
@@ -1551,12 +1661,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>5</v>
+      <c r="B44" t="s">
+        <v>175</v>
       </c>
       <c r="C44" s="1">
         <v>60</v>
@@ -1565,12 +1675,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>5</v>
+      <c r="B45" t="s">
+        <v>175</v>
       </c>
       <c r="C45" s="1">
         <v>60</v>
@@ -1579,12 +1689,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>5</v>
+      <c r="B46" t="s">
+        <v>175</v>
       </c>
       <c r="C46" s="1">
         <v>60</v>
@@ -1593,12 +1703,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>5</v>
+      <c r="B47" t="s">
+        <v>175</v>
       </c>
       <c r="C47" s="1">
         <v>60</v>
@@ -1607,12 +1717,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>5</v>
+      <c r="B48" t="s">
+        <v>175</v>
       </c>
       <c r="C48" s="1">
         <v>60</v>
@@ -1621,12 +1731,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>5</v>
+      <c r="B49" t="s">
+        <v>175</v>
       </c>
       <c r="C49" s="1">
         <v>60</v>
@@ -1635,12 +1745,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>5</v>
+      <c r="B50" t="s">
+        <v>175</v>
       </c>
       <c r="C50" s="1">
         <v>60</v>
@@ -1649,12 +1759,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>5</v>
+      <c r="B51" t="s">
+        <v>175</v>
       </c>
       <c r="C51" s="1">
         <v>60</v>
@@ -1663,12 +1773,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>5</v>
+      <c r="B52" t="s">
+        <v>175</v>
       </c>
       <c r="C52" s="1">
         <v>60</v>
@@ -1677,12 +1787,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>5</v>
+      <c r="B53" t="s">
+        <v>175</v>
       </c>
       <c r="C53" s="1">
         <v>60</v>
@@ -1691,12 +1801,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>5</v>
+      <c r="B54" t="s">
+        <v>175</v>
       </c>
       <c r="C54" s="1">
         <v>60</v>
@@ -1705,12 +1815,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>5</v>
+      <c r="B55" t="s">
+        <v>175</v>
       </c>
       <c r="C55" s="1">
         <v>60</v>
@@ -1719,12 +1829,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>5</v>
+      <c r="B56" t="s">
+        <v>175</v>
       </c>
       <c r="C56" s="1">
         <v>60</v>
@@ -1733,12 +1843,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>5</v>
+      <c r="B57" t="s">
+        <v>175</v>
       </c>
       <c r="C57" s="1">
         <v>60</v>
@@ -1747,12 +1857,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>5</v>
+      <c r="B58" t="s">
+        <v>175</v>
       </c>
       <c r="C58" s="1">
         <v>60</v>
@@ -1761,12 +1871,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>5</v>
+      <c r="B59" t="s">
+        <v>175</v>
       </c>
       <c r="C59" s="1">
         <v>60</v>
@@ -1775,12 +1885,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>5</v>
+      <c r="B60" t="s">
+        <v>175</v>
       </c>
       <c r="C60" s="1">
         <v>60</v>
@@ -1789,12 +1899,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>5</v>
+      <c r="B61" t="s">
+        <v>175</v>
       </c>
       <c r="C61" s="1">
         <v>60</v>
@@ -1803,12 +1913,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>5</v>
+      <c r="B62" t="s">
+        <v>175</v>
       </c>
       <c r="C62" s="1">
         <v>60</v>
@@ -1817,12 +1927,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>5</v>
+      <c r="B63" t="s">
+        <v>175</v>
       </c>
       <c r="C63" s="1">
         <v>60</v>
@@ -1831,12 +1941,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>5</v>
+      <c r="B64" t="s">
+        <v>175</v>
       </c>
       <c r="C64" s="1">
         <v>60</v>
@@ -1845,12 +1955,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>5</v>
+      <c r="B65" t="s">
+        <v>175</v>
       </c>
       <c r="C65" s="1">
         <v>60</v>
@@ -1859,12 +1969,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>5</v>
+      <c r="B66" t="s">
+        <v>175</v>
       </c>
       <c r="C66" s="1">
         <v>60</v>
@@ -1873,12 +1983,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>5</v>
+      <c r="B67" t="s">
+        <v>175</v>
       </c>
       <c r="C67" s="1">
         <v>60</v>
@@ -1887,12 +1997,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>5</v>
+      <c r="B68" t="s">
+        <v>175</v>
       </c>
       <c r="C68" s="1">
         <v>60</v>
@@ -1901,12 +2011,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>5</v>
+      <c r="B69" t="s">
+        <v>175</v>
       </c>
       <c r="C69" s="1">
         <v>60</v>
@@ -1915,12 +2025,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>5</v>
+      <c r="B70" t="s">
+        <v>175</v>
       </c>
       <c r="C70" s="1">
         <v>60</v>
@@ -1929,12 +2039,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>5</v>
+      <c r="B71" t="s">
+        <v>175</v>
       </c>
       <c r="C71" s="1">
         <v>60</v>
@@ -1943,12 +2053,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>5</v>
+      <c r="B72" t="s">
+        <v>175</v>
       </c>
       <c r="C72" s="1">
         <v>60</v>
@@ -1957,12 +2067,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>5</v>
+      <c r="B73" t="s">
+        <v>175</v>
       </c>
       <c r="C73" s="1">
         <v>60</v>
@@ -1971,12 +2081,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>5</v>
+      <c r="B74" t="s">
+        <v>175</v>
       </c>
       <c r="C74" s="1">
         <v>60</v>
@@ -1985,12 +2095,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>5</v>
+      <c r="B75" t="s">
+        <v>175</v>
       </c>
       <c r="C75" s="1">
         <v>60</v>
@@ -1999,12 +2109,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>5</v>
+      <c r="B76" t="s">
+        <v>175</v>
       </c>
       <c r="C76" s="1">
         <v>60</v>
@@ -2013,12 +2123,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>5</v>
+      <c r="B77" t="s">
+        <v>175</v>
       </c>
       <c r="C77" s="1">
         <v>60</v>
@@ -2027,12 +2137,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>5</v>
+      <c r="B78" t="s">
+        <v>175</v>
       </c>
       <c r="C78" s="1">
         <v>60</v>
@@ -2041,12 +2151,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>5</v>
+      <c r="B79" t="s">
+        <v>175</v>
       </c>
       <c r="C79" s="1">
         <v>60</v>
@@ -2055,12 +2165,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>5</v>
+      <c r="B80" t="s">
+        <v>175</v>
       </c>
       <c r="C80" s="1">
         <v>60</v>
@@ -2069,12 +2179,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>5</v>
+      <c r="B81" t="s">
+        <v>175</v>
       </c>
       <c r="C81" s="1">
         <v>60</v>
@@ -2083,12 +2193,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>5</v>
+      <c r="B82" t="s">
+        <v>175</v>
       </c>
       <c r="C82" s="1">
         <v>60</v>
@@ -2097,12 +2207,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>5</v>
+      <c r="B83" t="s">
+        <v>175</v>
       </c>
       <c r="C83" s="1">
         <v>60</v>
@@ -2111,12 +2221,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>5</v>
+      <c r="B84" t="s">
+        <v>175</v>
       </c>
       <c r="C84" s="1">
         <v>60</v>
@@ -2125,12 +2235,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>5</v>
+      <c r="B85" t="s">
+        <v>175</v>
       </c>
       <c r="C85" s="1">
         <v>60</v>
@@ -2139,12 +2249,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>5</v>
+      <c r="B86" t="s">
+        <v>175</v>
       </c>
       <c r="C86" s="1">
         <v>60</v>
@@ -2153,12 +2263,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>5</v>
+      <c r="B87" t="s">
+        <v>175</v>
       </c>
       <c r="C87" s="1">
         <v>60</v>
@@ -2167,12 +2277,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>5</v>
+      <c r="B88" t="s">
+        <v>175</v>
       </c>
       <c r="C88" s="1">
         <v>60</v>
@@ -2181,12 +2291,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>5</v>
+      <c r="B89" t="s">
+        <v>175</v>
       </c>
       <c r="C89" s="1">
         <v>60</v>
@@ -2195,12 +2305,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>5</v>
+      <c r="B90" t="s">
+        <v>175</v>
       </c>
       <c r="C90" s="1">
         <v>60</v>
@@ -2209,12 +2319,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>5</v>
+      <c r="B91" t="s">
+        <v>175</v>
       </c>
       <c r="C91" s="1">
         <v>60</v>
@@ -2223,12 +2333,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>5</v>
+      <c r="B92" t="s">
+        <v>175</v>
       </c>
       <c r="C92" s="1">
         <v>60</v>
@@ -2237,12 +2347,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>5</v>
+      <c r="B93" t="s">
+        <v>175</v>
       </c>
       <c r="C93" s="1">
         <v>60</v>
@@ -2251,12 +2361,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>5</v>
+      <c r="B94" t="s">
+        <v>175</v>
       </c>
       <c r="C94" s="1">
         <v>60</v>
@@ -2265,12 +2375,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>5</v>
+      <c r="B95" t="s">
+        <v>175</v>
       </c>
       <c r="C95" s="1">
         <v>60</v>
@@ -2279,12 +2389,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>5</v>
+      <c r="B96" t="s">
+        <v>175</v>
       </c>
       <c r="C96" s="1">
         <v>60</v>
@@ -2293,12 +2403,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>5</v>
+      <c r="B97" t="s">
+        <v>175</v>
       </c>
       <c r="C97" s="1">
         <v>60</v>
@@ -2307,12 +2417,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>5</v>
+      <c r="B98" t="s">
+        <v>175</v>
       </c>
       <c r="C98" s="1">
         <v>60</v>
@@ -2321,12 +2431,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>5</v>
+      <c r="B99" t="s">
+        <v>175</v>
       </c>
       <c r="C99" s="1">
         <v>60</v>
@@ -2335,12 +2445,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>5</v>
+      <c r="B100" t="s">
+        <v>175</v>
       </c>
       <c r="C100" s="1">
         <v>60</v>
@@ -2349,12 +2459,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>5</v>
+      <c r="B101" t="s">
+        <v>175</v>
       </c>
       <c r="C101" s="1">
         <v>60</v>
@@ -2363,12 +2473,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>5</v>
+      <c r="B102" t="s">
+        <v>175</v>
       </c>
       <c r="C102" s="1">
         <v>60</v>
@@ -2377,12 +2487,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>5</v>
+      <c r="B103" t="s">
+        <v>175</v>
       </c>
       <c r="C103" s="1">
         <v>60</v>
@@ -2391,12 +2501,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>5</v>
+      <c r="B104" t="s">
+        <v>175</v>
       </c>
       <c r="C104" s="1">
         <v>60</v>
@@ -2405,12 +2515,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>5</v>
+      <c r="B105" t="s">
+        <v>175</v>
       </c>
       <c r="C105" s="1">
         <v>60</v>
@@ -2419,12 +2529,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>5</v>
+      <c r="B106" t="s">
+        <v>175</v>
       </c>
       <c r="C106" s="1">
         <v>60</v>
@@ -2433,12 +2543,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>5</v>
+      <c r="B107" t="s">
+        <v>175</v>
       </c>
       <c r="C107" s="1">
         <v>60</v>
@@ -2447,12 +2557,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>5</v>
+      <c r="B108" t="s">
+        <v>175</v>
       </c>
       <c r="C108" s="1">
         <v>60</v>
@@ -2461,12 +2571,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>5</v>
+      <c r="B109" t="s">
+        <v>175</v>
       </c>
       <c r="C109" s="1">
         <v>60</v>
@@ -2475,12 +2585,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>5</v>
+      <c r="B110" t="s">
+        <v>175</v>
       </c>
       <c r="C110" s="1">
         <v>60</v>
@@ -2489,12 +2599,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>5</v>
+      <c r="B111" t="s">
+        <v>175</v>
       </c>
       <c r="C111" s="1">
         <v>60</v>
@@ -2503,12 +2613,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>5</v>
+      <c r="B112" t="s">
+        <v>175</v>
       </c>
       <c r="C112" s="1">
         <v>60</v>
@@ -2517,12 +2627,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>5</v>
+      <c r="B113" t="s">
+        <v>175</v>
       </c>
       <c r="C113" s="1">
         <v>60</v>
@@ -2531,12 +2641,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>5</v>
+      <c r="B114" t="s">
+        <v>175</v>
       </c>
       <c r="C114" s="1">
         <v>60</v>
@@ -2545,12 +2655,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>5</v>
+      <c r="B115" t="s">
+        <v>175</v>
       </c>
       <c r="C115" s="1">
         <v>60</v>
@@ -2559,12 +2669,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>5</v>
+      <c r="B116" t="s">
+        <v>175</v>
       </c>
       <c r="C116" s="1">
         <v>60</v>
@@ -2573,12 +2683,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>5</v>
+      <c r="B117" t="s">
+        <v>175</v>
       </c>
       <c r="C117" s="1">
         <v>60</v>
@@ -2587,12 +2697,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>5</v>
+      <c r="B118" t="s">
+        <v>175</v>
       </c>
       <c r="C118" s="1">
         <v>60</v>
@@ -2601,12 +2711,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>5</v>
+      <c r="B119" t="s">
+        <v>175</v>
       </c>
       <c r="C119" s="1">
         <v>60</v>
@@ -2615,12 +2725,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>5</v>
+      <c r="B120" t="s">
+        <v>175</v>
       </c>
       <c r="C120" s="1">
         <v>60</v>
@@ -2629,12 +2739,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>5</v>
+      <c r="B121" t="s">
+        <v>175</v>
       </c>
       <c r="C121" s="1">
         <v>60</v>
@@ -2643,12 +2753,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>5</v>
+      <c r="B122" t="s">
+        <v>175</v>
       </c>
       <c r="C122" s="1">
         <v>60</v>
@@ -2657,12 +2767,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>5</v>
+      <c r="B123" t="s">
+        <v>175</v>
       </c>
       <c r="C123" s="1">
         <v>60</v>
@@ -2671,12 +2781,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>5</v>
+      <c r="B124" t="s">
+        <v>175</v>
       </c>
       <c r="C124" s="1">
         <v>60</v>
@@ -2685,12 +2795,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>5</v>
+      <c r="B125" t="s">
+        <v>175</v>
       </c>
       <c r="C125" s="1">
         <v>60</v>
@@ -2699,12 +2809,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>5</v>
+      <c r="B126" t="s">
+        <v>175</v>
       </c>
       <c r="C126" s="1">
         <v>60</v>
@@ -2713,12 +2823,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>5</v>
+      <c r="B127" t="s">
+        <v>175</v>
       </c>
       <c r="C127" s="1">
         <v>60</v>
@@ -2727,12 +2837,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>5</v>
+      <c r="B128" t="s">
+        <v>175</v>
       </c>
       <c r="C128" s="1">
         <v>60</v>
@@ -2741,12 +2851,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>5</v>
+      <c r="B129" t="s">
+        <v>175</v>
       </c>
       <c r="C129" s="1">
         <v>60</v>
@@ -2755,12 +2865,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>5</v>
+      <c r="B130" t="s">
+        <v>175</v>
       </c>
       <c r="C130" s="1">
         <v>60</v>
@@ -2769,12 +2879,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>5</v>
+      <c r="B131" t="s">
+        <v>175</v>
       </c>
       <c r="C131" s="1">
         <v>60</v>
@@ -2783,12 +2893,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>5</v>
+      <c r="B132" t="s">
+        <v>175</v>
       </c>
       <c r="C132" s="1">
         <v>60</v>
@@ -2797,12 +2907,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>5</v>
+      <c r="B133" t="s">
+        <v>175</v>
       </c>
       <c r="C133" s="1">
         <v>60</v>
@@ -2811,12 +2921,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>5</v>
+      <c r="B134" t="s">
+        <v>175</v>
       </c>
       <c r="C134" s="1">
         <v>60</v>
@@ -2825,12 +2935,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>5</v>
+      <c r="B135" t="s">
+        <v>175</v>
       </c>
       <c r="C135" s="1">
         <v>60</v>
@@ -2839,12 +2949,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>5</v>
+      <c r="B136" t="s">
+        <v>175</v>
       </c>
       <c r="C136" s="1">
         <v>60</v>
@@ -2853,12 +2963,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>5</v>
+      <c r="B137" t="s">
+        <v>175</v>
       </c>
       <c r="C137" s="1">
         <v>60</v>
@@ -2867,12 +2977,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>5</v>
+      <c r="B138" t="s">
+        <v>175</v>
       </c>
       <c r="C138" s="1">
         <v>60</v>
@@ -2881,12 +2991,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>5</v>
+      <c r="B139" t="s">
+        <v>175</v>
       </c>
       <c r="C139" s="1">
         <v>60</v>
@@ -2895,12 +3005,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>5</v>
+      <c r="B140" t="s">
+        <v>175</v>
       </c>
       <c r="C140" s="1">
         <v>60</v>
@@ -2909,12 +3019,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>5</v>
+      <c r="B141" t="s">
+        <v>175</v>
       </c>
       <c r="C141" s="1">
         <v>60</v>
@@ -2923,12 +3033,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>5</v>
+      <c r="B142" t="s">
+        <v>175</v>
       </c>
       <c r="C142" s="1">
         <v>60</v>
@@ -2937,12 +3047,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>5</v>
+      <c r="B143" t="s">
+        <v>175</v>
       </c>
       <c r="C143" s="1">
         <v>60</v>
@@ -2951,12 +3061,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>5</v>
+      <c r="B144" t="s">
+        <v>175</v>
       </c>
       <c r="C144" s="1">
         <v>60</v>
@@ -2965,12 +3075,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>5</v>
+      <c r="B145" t="s">
+        <v>175</v>
       </c>
       <c r="C145" s="1">
         <v>60</v>
@@ -2979,12 +3089,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>5</v>
+      <c r="B146" t="s">
+        <v>175</v>
       </c>
       <c r="C146" s="1">
         <v>60</v>
@@ -2993,12 +3103,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>5</v>
+      <c r="B147" t="s">
+        <v>175</v>
       </c>
       <c r="C147" s="1">
         <v>60</v>
@@ -3007,12 +3117,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>5</v>
+      <c r="B148" t="s">
+        <v>175</v>
       </c>
       <c r="C148" s="1">
         <v>60</v>
@@ -3021,12 +3131,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>5</v>
+      <c r="B149" t="s">
+        <v>175</v>
       </c>
       <c r="C149" s="1">
         <v>60</v>
@@ -3035,12 +3145,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>5</v>
+      <c r="B150" t="s">
+        <v>175</v>
       </c>
       <c r="C150" s="1">
         <v>60</v>
@@ -3049,12 +3159,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>5</v>
+      <c r="B151" t="s">
+        <v>175</v>
       </c>
       <c r="C151" s="1">
         <v>60</v>
@@ -3063,12 +3173,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>5</v>
+      <c r="B152" t="s">
+        <v>175</v>
       </c>
       <c r="C152" s="1">
         <v>60</v>
@@ -3077,12 +3187,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>5</v>
+      <c r="B153" t="s">
+        <v>175</v>
       </c>
       <c r="C153" s="1">
         <v>60</v>
@@ -3091,12 +3201,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>5</v>
+      <c r="B154" t="s">
+        <v>175</v>
       </c>
       <c r="C154" s="1">
         <v>60</v>
@@ -3105,12 +3215,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>5</v>
+      <c r="B155" t="s">
+        <v>175</v>
       </c>
       <c r="C155" s="1">
         <v>60</v>
@@ -3119,12 +3229,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>5</v>
+      <c r="B156" t="s">
+        <v>175</v>
       </c>
       <c r="C156" s="1">
         <v>60</v>
@@ -3133,12 +3243,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>5</v>
+      <c r="B157" t="s">
+        <v>175</v>
       </c>
       <c r="C157" s="1">
         <v>60</v>
@@ -3147,12 +3257,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>5</v>
+      <c r="B158" t="s">
+        <v>175</v>
       </c>
       <c r="C158" s="1">
         <v>60</v>
@@ -3161,12 +3271,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>5</v>
+      <c r="B159" t="s">
+        <v>175</v>
       </c>
       <c r="C159" s="1">
         <v>60</v>
@@ -3175,12 +3285,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>5</v>
+      <c r="B160" t="s">
+        <v>175</v>
       </c>
       <c r="C160" s="1">
         <v>60</v>
@@ -3189,12 +3299,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>5</v>
+      <c r="B161" t="s">
+        <v>175</v>
       </c>
       <c r="C161" s="1">
         <v>60</v>
